--- a/AAII_Financials/Quarterly/UPC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
   <si>
     <t>UPC</t>
   </si>
@@ -656,69 +656,70 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44469</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44104</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43921</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43738</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43555</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -731,41 +732,44 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E8" s="3">
         <v>18500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>48000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>30700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -778,41 +782,44 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E9" s="3">
         <v>12300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>22700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>19600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11100</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -825,41 +832,44 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E10" s="3">
         <v>6200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>25300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>12000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>14100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -872,8 +882,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,41 +904,42 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E12" s="3">
         <v>2300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -938,8 +952,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,8 +1002,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1011,12 +1031,12 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1032,8 +1052,11 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1046,27 +1069,27 @@
       <c r="F15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3">
         <v>200</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="I15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3">
         <v>200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1079,8 +1102,11 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,41 +1121,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>17500</v>
       </c>
       <c r="E17" s="3">
+        <v>18300</v>
+      </c>
+      <c r="F17" s="3">
         <v>26100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>34400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12900</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1142,41 +1169,44 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-3700</v>
       </c>
       <c r="E18" s="3">
+        <v>200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-10200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5200</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1189,8 +1219,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,26 +1241,27 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-400</v>
       </c>
       <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1235,13 +1269,13 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>100</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1255,41 +1289,44 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-3900</v>
       </c>
       <c r="E21" s="3">
+        <v>500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-11100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1302,8 +1339,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1316,14 +1356,14 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
@@ -1334,8 +1374,8 @@
       <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>100</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
@@ -1349,41 +1389,44 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E23" s="3">
         <v>300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5200</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1396,41 +1439,44 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
-      </c>
-      <c r="G24" s="3">
-        <v>2400</v>
       </c>
       <c r="H24" s="3">
         <v>2400</v>
       </c>
       <c r="I24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J24" s="3">
         <v>2500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1443,8 +1489,11 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,41 +1539,44 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-5400</v>
       </c>
       <c r="E26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-10500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4100</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1537,41 +1589,44 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-5400</v>
       </c>
       <c r="E27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-10500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4100</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,8 +1639,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1689,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1739,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1789,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,26 +1839,29 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>400</v>
       </c>
       <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -1799,13 +1869,13 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>-100</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1819,41 +1889,44 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-5400</v>
       </c>
       <c r="E33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-10500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1866,8 +1939,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,41 +1989,44 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-5400</v>
       </c>
       <c r="E35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-10500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1960,46 +2039,49 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44469</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44104</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43921</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43738</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43555</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2012,8 +2094,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2116,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,32 +2136,33 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E41" s="3">
         <v>13000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
+        <v>5700</v>
+      </c>
+      <c r="G41" s="3">
         <v>14200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>36000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>10100</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2097,31 +2184,34 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>13200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>13300</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>13100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>14300</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+        <v>13700</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2144,32 +2234,35 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E43" s="3">
         <v>17500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
+        <v>15200</v>
+      </c>
+      <c r="G43" s="3">
         <v>18800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>15600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>17800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>10900</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2191,32 +2284,35 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E44" s="3">
         <v>2900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G44" s="3">
         <v>3400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>4900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1900</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2238,32 +2334,35 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>19200</v>
+        <v>4300</v>
       </c>
       <c r="E45" s="3">
-        <v>15200</v>
+        <v>5900</v>
       </c>
       <c r="F45" s="3">
-        <v>24400</v>
+        <v>5300</v>
       </c>
       <c r="G45" s="3">
+        <v>900</v>
+      </c>
+      <c r="H45" s="3">
+        <v>10600</v>
+      </c>
+      <c r="I45" s="3">
         <v>3100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,32 +2384,35 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E46" s="3">
         <v>52500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
+        <v>41500</v>
+      </c>
+      <c r="G46" s="3">
         <v>51700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>50500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>61800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>23300</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2332,8 +2434,11 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2341,22 +2446,22 @@
         <v>700</v>
       </c>
       <c r="E47" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F47" s="3">
         <v>700</v>
       </c>
       <c r="G47" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="H47" s="3">
         <v>700</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+      <c r="I47" s="3">
+        <v>800</v>
+      </c>
+      <c r="J47" s="3">
+        <v>700</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -2379,32 +2484,35 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E48" s="3">
         <v>13800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>13600</v>
+      </c>
+      <c r="G48" s="3">
         <v>15400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>15400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>4400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4400</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2426,13 +2534,16 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
         <v>200</v>
@@ -2446,11 +2557,11 @@
       <c r="H49" s="3">
         <v>200</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="I49" s="3">
+        <v>200</v>
+      </c>
+      <c r="J49" s="3">
+        <v>200</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2473,8 +2584,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2634,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,32 +2684,35 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E52" s="3">
         <v>3200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G52" s="3">
         <v>3500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2614,8 +2734,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,32 +2784,35 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>53300</v>
+      </c>
+      <c r="E54" s="3">
         <v>70400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
+        <v>59500</v>
+      </c>
+      <c r="G54" s="3">
         <v>71400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>70100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>67300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>28800</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2708,8 +2834,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2856,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,32 +2876,33 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E57" s="3">
         <v>11200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>5300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>8600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,31 +2924,34 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9500</v>
+        <v>5500</v>
       </c>
       <c r="E58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F58" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G58" s="3">
         <v>4400</v>
       </c>
-      <c r="F58" s="3">
-        <v>4400</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5900</v>
-      </c>
       <c r="H58" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>4300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J58" s="3">
+        <v>2600</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2840,31 +2974,34 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2500</v>
+        <v>3700</v>
       </c>
       <c r="E59" s="3">
-        <v>2100</v>
+        <v>7900</v>
       </c>
       <c r="F59" s="3">
-        <v>1500</v>
+        <v>6100</v>
       </c>
       <c r="G59" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="H59" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>1600</v>
+      </c>
+      <c r="I59" s="3">
+        <v>5200</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2700</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2887,32 +3024,35 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E60" s="3">
         <v>23200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
+        <v>13100</v>
+      </c>
+      <c r="G60" s="3">
         <v>10200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>11200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>16600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>8000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2934,8 +3074,11 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2981,8 +3124,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3028,8 +3174,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3224,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3274,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,32 +3324,35 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>3</v>
+      <c r="D66" s="3">
+        <v>13800</v>
       </c>
       <c r="E66" s="3">
+        <v>23200</v>
+      </c>
+      <c r="F66" s="3">
+        <v>13100</v>
+      </c>
+      <c r="G66" s="3">
         <v>10200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>11200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>16600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>8000</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3216,8 +3374,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3396,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3444,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3494,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3544,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,32 +3594,35 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E72" s="3">
         <v>18000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
+        <v>18800</v>
+      </c>
+      <c r="G72" s="3">
         <v>29200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>27500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>23300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>16200</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3644,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3694,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3744,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,32 +3794,35 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E76" s="3">
         <v>47100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
+        <v>46400</v>
+      </c>
+      <c r="G76" s="3">
         <v>61200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>58900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>50700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>20800</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3658,8 +3844,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,46 +3894,49 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44469</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44104</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43921</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43738</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43555</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3757,41 +3949,44 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-5400</v>
       </c>
       <c r="E81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-10500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3804,8 +3999,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,41 +4021,42 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>300</v>
       </c>
       <c r="E83" s="3">
+        <v>300</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3870,8 +4069,11 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4119,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4169,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4219,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4269,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,41 +4319,44 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-3700</v>
       </c>
       <c r="E89" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-7400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7700</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4152,8 +4369,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,8 +4391,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4180,31 +4401,31 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
@@ -4218,8 +4439,11 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4489,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,40 +4539,43 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-100</v>
       </c>
       <c r="I94" s="3">
         <v>-100</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
@@ -4359,8 +4589,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4611,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4425,8 +4659,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4709,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4759,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,41 +4809,44 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-100</v>
+        <v>-3500</v>
       </c>
       <c r="E100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F100" s="3">
         <v>3300</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>26600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>24100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-16000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4613,41 +4859,44 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E101" s="3">
+        <v>400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-100</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
       </c>
       <c r="L101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M101" s="3">
         <v>200</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4660,41 +4909,44 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>-7700</v>
       </c>
       <c r="E102" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-8500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>25900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,6 +4957,9 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="92">
   <si>
     <t>UPC</t>
   </si>
@@ -656,76 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
-        <v>44651</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44469</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44286</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44104</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>43921</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43738</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43555</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -735,47 +735,53 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>13800</v>
+        <v>6400</v>
       </c>
       <c r="E8" s="3">
-        <v>18500</v>
+        <v>6400</v>
       </c>
       <c r="F8" s="3">
-        <v>15900</v>
+        <v>6900</v>
       </c>
       <c r="G8" s="3">
-        <v>24200</v>
+        <v>6900</v>
       </c>
       <c r="H8" s="3">
-        <v>48000</v>
+        <v>9200</v>
       </c>
       <c r="I8" s="3">
+        <v>9200</v>
+      </c>
+      <c r="J8" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K8" s="3">
         <v>24300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>30700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>16400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>33200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>18100</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -785,47 +791,53 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>9700</v>
+        <v>4800</v>
       </c>
       <c r="E9" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F9" s="3">
+        <v>4800</v>
+      </c>
+      <c r="G9" s="3">
+        <v>4800</v>
+      </c>
+      <c r="H9" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J9" s="3">
+        <v>3900</v>
+      </c>
+      <c r="K9" s="3">
         <v>12300</v>
       </c>
-      <c r="F9" s="3">
-        <v>7800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>10400</v>
-      </c>
-      <c r="H9" s="3">
-        <v>22700</v>
-      </c>
-      <c r="I9" s="3">
-        <v>12300</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>16600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>7900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>19600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>11100</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -835,47 +847,53 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J10" s="3">
         <v>4100</v>
       </c>
-      <c r="E10" s="3">
-        <v>6200</v>
-      </c>
-      <c r="F10" s="3">
-        <v>8100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>13800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>25300</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>12000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>14100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>8500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>13600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>7000</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -885,8 +903,14 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -905,47 +929,49 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="E12" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3">
-        <v>7500</v>
+        <v>1300</v>
       </c>
       <c r="G12" s="3">
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="H12" s="3">
-        <v>5400</v>
+        <v>1100</v>
       </c>
       <c r="I12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K12" s="3">
         <v>300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>600</v>
-      </c>
-      <c r="K12" s="3">
-        <v>500</v>
       </c>
       <c r="L12" s="3">
         <v>600</v>
       </c>
       <c r="M12" s="3">
+        <v>500</v>
+      </c>
+      <c r="N12" s="3">
+        <v>600</v>
+      </c>
+      <c r="O12" s="3">
         <v>300</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -955,8 +981,14 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1005,44 +1037,50 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>200</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1055,34 +1093,40 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>100</v>
+      </c>
+      <c r="G15" s="3">
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>200</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
-      </c>
-      <c r="K15" s="3">
         <v>100</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L15" s="3">
         <v>200</v>
@@ -1090,11 +1134,11 @@
       <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="N15" s="3">
+        <v>200</v>
+      </c>
+      <c r="O15" s="3">
+        <v>100</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
@@ -1105,8 +1149,14 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,47 +1172,49 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17500</v>
+        <v>7300</v>
       </c>
       <c r="E17" s="3">
-        <v>18300</v>
+        <v>7300</v>
       </c>
       <c r="F17" s="3">
-        <v>26100</v>
+        <v>8800</v>
       </c>
       <c r="G17" s="3">
-        <v>21500</v>
+        <v>8800</v>
       </c>
       <c r="H17" s="3">
-        <v>34400</v>
+        <v>9200</v>
       </c>
       <c r="I17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="J17" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K17" s="3">
         <v>14700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>20500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>9800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>23500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>12900</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1172,47 +1224,53 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3700</v>
+        <v>-900</v>
       </c>
       <c r="E18" s="3">
-        <v>200</v>
+        <v>-900</v>
       </c>
       <c r="F18" s="3">
-        <v>-10200</v>
+        <v>-1800</v>
       </c>
       <c r="G18" s="3">
-        <v>2700</v>
+        <v>-1800</v>
       </c>
       <c r="H18" s="3">
-        <v>13600</v>
+        <v>100</v>
       </c>
       <c r="I18" s="3">
+        <v>100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="K18" s="3">
         <v>9600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>10200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>6600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>9700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>5200</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1222,8 +1280,14 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,25 +1306,27 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>-1100</v>
-      </c>
       <c r="G20" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1272,17 +1338,17 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1292,47 +1358,53 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3900</v>
+        <v>-700</v>
       </c>
       <c r="E21" s="3">
-        <v>500</v>
+        <v>-700</v>
       </c>
       <c r="F21" s="3">
-        <v>-11100</v>
+        <v>-1800</v>
       </c>
       <c r="G21" s="3">
-        <v>3600</v>
+        <v>-1800</v>
       </c>
       <c r="H21" s="3">
-        <v>14200</v>
+        <v>200</v>
       </c>
       <c r="I21" s="3">
+        <v>200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="K21" s="3">
         <v>9800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>10600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>6800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>10200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>5500</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1342,34 +1414,40 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>100</v>
+      </c>
+      <c r="F22" s="3">
+        <v>100</v>
+      </c>
+      <c r="G22" s="3">
+        <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>100</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3">
-        <v>100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
@@ -1377,11 +1455,11 @@
       <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>100</v>
+      </c>
+      <c r="O22" s="3">
+        <v>100</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
@@ -1392,47 +1470,53 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-4100</v>
+        <v>-6200</v>
       </c>
       <c r="E23" s="3">
-        <v>300</v>
+        <v>-6200</v>
       </c>
       <c r="F23" s="3">
-        <v>-11300</v>
+        <v>-2100</v>
       </c>
       <c r="G23" s="3">
-        <v>3300</v>
+        <v>-2100</v>
       </c>
       <c r="H23" s="3">
-        <v>13700</v>
+        <v>100</v>
       </c>
       <c r="I23" s="3">
+        <v>100</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="K23" s="3">
         <v>9600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>10100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>6500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>9700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>5200</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1442,47 +1526,53 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1300</v>
+        <v>300</v>
       </c>
       <c r="E24" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="F24" s="3">
-        <v>-800</v>
+        <v>700</v>
       </c>
       <c r="G24" s="3">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="H24" s="3">
+        <v>500</v>
+      </c>
+      <c r="I24" s="3">
+        <v>500</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K24" s="3">
         <v>2400</v>
       </c>
-      <c r="I24" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>2100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1100</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1492,8 +1582,14 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1542,47 +1638,53 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-5400</v>
+        <v>-6600</v>
       </c>
       <c r="E26" s="3">
-        <v>-700</v>
+        <v>-6600</v>
       </c>
       <c r="F26" s="3">
-        <v>-10500</v>
+        <v>-2700</v>
       </c>
       <c r="G26" s="3">
-        <v>1700</v>
+        <v>-2700</v>
       </c>
       <c r="H26" s="3">
-        <v>11300</v>
+        <v>-400</v>
       </c>
       <c r="I26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K26" s="3">
         <v>7100</v>
-      </c>
-      <c r="J26" s="3">
-        <v>7600</v>
-      </c>
-      <c r="K26" s="3">
-        <v>5100</v>
       </c>
       <c r="L26" s="3">
         <v>7600</v>
       </c>
       <c r="M26" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N26" s="3">
+        <v>7600</v>
+      </c>
+      <c r="O26" s="3">
         <v>4100</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1592,47 +1694,53 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-5400</v>
+        <v>-6600</v>
       </c>
       <c r="E27" s="3">
-        <v>-700</v>
+        <v>-6600</v>
       </c>
       <c r="F27" s="3">
-        <v>-10500</v>
+        <v>-2700</v>
       </c>
       <c r="G27" s="3">
-        <v>1700</v>
+        <v>-2700</v>
       </c>
       <c r="H27" s="3">
-        <v>11300</v>
+        <v>-400</v>
       </c>
       <c r="I27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K27" s="3">
         <v>7100</v>
-      </c>
-      <c r="J27" s="3">
-        <v>7600</v>
-      </c>
-      <c r="K27" s="3">
-        <v>5100</v>
       </c>
       <c r="L27" s="3">
         <v>7600</v>
       </c>
       <c r="M27" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N27" s="3">
+        <v>7600</v>
+      </c>
+      <c r="O27" s="3">
         <v>4100</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1642,8 +1750,14 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1692,8 +1806,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1742,8 +1862,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1792,8 +1918,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1842,25 +1974,31 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>1100</v>
-      </c>
       <c r="G32" s="3">
-        <v>-600</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -1872,17 +2010,17 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1892,47 +2030,53 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-5400</v>
+        <v>-6600</v>
       </c>
       <c r="E33" s="3">
-        <v>-700</v>
+        <v>-6600</v>
       </c>
       <c r="F33" s="3">
-        <v>-10500</v>
+        <v>-2700</v>
       </c>
       <c r="G33" s="3">
-        <v>1700</v>
+        <v>-2700</v>
       </c>
       <c r="H33" s="3">
-        <v>11300</v>
+        <v>-400</v>
       </c>
       <c r="I33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K33" s="3">
         <v>7100</v>
-      </c>
-      <c r="J33" s="3">
-        <v>7600</v>
-      </c>
-      <c r="K33" s="3">
-        <v>5100</v>
       </c>
       <c r="L33" s="3">
         <v>7600</v>
       </c>
       <c r="M33" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N33" s="3">
+        <v>7600</v>
+      </c>
+      <c r="O33" s="3">
         <v>4100</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1942,8 +2086,14 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1992,47 +2142,53 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-5400</v>
+        <v>-6600</v>
       </c>
       <c r="E35" s="3">
-        <v>-700</v>
+        <v>-6600</v>
       </c>
       <c r="F35" s="3">
-        <v>-10500</v>
+        <v>-2700</v>
       </c>
       <c r="G35" s="3">
-        <v>1700</v>
+        <v>-2700</v>
       </c>
       <c r="H35" s="3">
-        <v>11300</v>
+        <v>-400</v>
       </c>
       <c r="I35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K35" s="3">
         <v>7100</v>
-      </c>
-      <c r="J35" s="3">
-        <v>7600</v>
-      </c>
-      <c r="K35" s="3">
-        <v>5100</v>
       </c>
       <c r="L35" s="3">
         <v>7600</v>
       </c>
       <c r="M35" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N35" s="3">
+        <v>7600</v>
+      </c>
+      <c r="O35" s="3">
         <v>4100</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2042,52 +2198,58 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
-        <v>44651</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44469</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44286</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44104</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>43921</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43738</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43555</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2097,8 +2259,14 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2117,8 +2285,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2137,38 +2307,40 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F41" s="3">
         <v>5300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="H41" s="3">
         <v>13000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J41" s="3">
         <v>5700</v>
       </c>
-      <c r="G41" s="3">
-        <v>14200</v>
-      </c>
-      <c r="H41" s="3">
-        <v>8100</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>36000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>10100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2187,37 +2359,43 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F42" s="3">
         <v>13200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
+        <v>13200</v>
+      </c>
+      <c r="H42" s="3">
         <v>13300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="I42" s="3">
+        <v>13300</v>
+      </c>
+      <c r="J42" s="3">
         <v>13100</v>
       </c>
-      <c r="G42" s="3">
-        <v>14300</v>
-      </c>
-      <c r="H42" s="3">
-        <v>13700</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -2237,38 +2415,44 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>14400</v>
+      </c>
+      <c r="F43" s="3">
         <v>10700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
+        <v>10700</v>
+      </c>
+      <c r="H43" s="3">
         <v>17500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
+        <v>17500</v>
+      </c>
+      <c r="J43" s="3">
         <v>15200</v>
       </c>
-      <c r="G43" s="3">
-        <v>18800</v>
-      </c>
-      <c r="H43" s="3">
-        <v>15600</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>17800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>10900</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2287,38 +2471,44 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F44" s="3">
         <v>3300</v>
       </c>
-      <c r="E44" s="3">
-        <v>2900</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H44" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I44" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J44" s="3">
         <v>2200</v>
       </c>
-      <c r="G44" s="3">
-        <v>3400</v>
-      </c>
-      <c r="H44" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>4900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1900</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2337,38 +2527,44 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4300</v>
+        <v>400</v>
       </c>
       <c r="E45" s="3">
-        <v>5900</v>
+        <v>400</v>
       </c>
       <c r="F45" s="3">
-        <v>5300</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="H45" s="3">
-        <v>10600</v>
+        <v>3600</v>
       </c>
       <c r="I45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>3100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2387,38 +2583,44 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>33500</v>
+      </c>
+      <c r="F46" s="3">
         <v>36800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
+        <v>36800</v>
+      </c>
+      <c r="H46" s="3">
         <v>52500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
+        <v>52500</v>
+      </c>
+      <c r="J46" s="3">
         <v>41500</v>
       </c>
-      <c r="G46" s="3">
-        <v>51700</v>
-      </c>
-      <c r="H46" s="3">
-        <v>50500</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>61800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>23300</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2437,8 +2639,14 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2452,22 +2660,22 @@
         <v>700</v>
       </c>
       <c r="G47" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="H47" s="3">
         <v>700</v>
       </c>
       <c r="I47" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="J47" s="3">
         <v>700</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
+      <c r="K47" s="3">
+        <v>800</v>
+      </c>
+      <c r="L47" s="3">
+        <v>700</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
@@ -2487,38 +2695,44 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12800</v>
+        <v>3500</v>
       </c>
       <c r="E48" s="3">
-        <v>13800</v>
+        <v>3500</v>
       </c>
       <c r="F48" s="3">
-        <v>13600</v>
+        <v>3700</v>
       </c>
       <c r="G48" s="3">
-        <v>15400</v>
+        <v>3700</v>
       </c>
       <c r="H48" s="3">
-        <v>15400</v>
+        <v>4100</v>
       </c>
       <c r="I48" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J48" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K48" s="3">
         <v>4400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4400</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2537,8 +2751,14 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2546,13 +2766,13 @@
         <v>100</v>
       </c>
       <c r="E49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H49" s="3">
         <v>200</v>
@@ -2563,11 +2783,11 @@
       <c r="J49" s="3">
         <v>200</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>200</v>
+      </c>
+      <c r="L49" s="3">
+        <v>200</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2587,8 +2807,14 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2637,8 +2863,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2687,38 +2919,44 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2800</v>
+        <v>11500</v>
       </c>
       <c r="E52" s="3">
-        <v>3200</v>
+        <v>11500</v>
       </c>
       <c r="F52" s="3">
-        <v>3600</v>
+        <v>11300</v>
       </c>
       <c r="G52" s="3">
-        <v>3500</v>
+        <v>11300</v>
       </c>
       <c r="H52" s="3">
-        <v>3300</v>
+        <v>12000</v>
       </c>
       <c r="I52" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J52" s="3">
+        <v>11600</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2737,8 +2975,14 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2787,38 +3031,44 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>49400</v>
+      </c>
+      <c r="F54" s="3">
         <v>53300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>53300</v>
+      </c>
+      <c r="H54" s="3">
         <v>70400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
+        <v>70400</v>
+      </c>
+      <c r="J54" s="3">
         <v>59500</v>
       </c>
-      <c r="G54" s="3">
-        <v>71400</v>
-      </c>
-      <c r="H54" s="3">
-        <v>70100</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>67300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>28800</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2837,8 +3087,14 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2857,8 +3113,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2877,38 +3135,40 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F57" s="3">
         <v>4600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H57" s="3">
         <v>11200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
+        <v>11200</v>
+      </c>
+      <c r="J57" s="3">
         <v>3100</v>
       </c>
-      <c r="G57" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H57" s="3">
-        <v>5300</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>8600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2700</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2927,38 +3187,44 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F58" s="3">
         <v>5500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
+        <v>5500</v>
+      </c>
+      <c r="H58" s="3">
         <v>4100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
+        <v>4100</v>
+      </c>
+      <c r="J58" s="3">
         <v>3900</v>
       </c>
-      <c r="G58" s="3">
-        <v>4400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2600</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,38 +3243,44 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3700</v>
+        <v>5500</v>
       </c>
       <c r="E59" s="3">
-        <v>7900</v>
+        <v>5500</v>
       </c>
       <c r="F59" s="3">
-        <v>6100</v>
+        <v>500</v>
       </c>
       <c r="G59" s="3">
-        <v>2200</v>
+        <v>500</v>
       </c>
       <c r="H59" s="3">
-        <v>1600</v>
+        <v>5800</v>
       </c>
       <c r="I59" s="3">
+        <v>5800</v>
+      </c>
+      <c r="J59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K59" s="3">
         <v>5200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2700</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,38 +3299,44 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F60" s="3">
         <v>13800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
+        <v>13800</v>
+      </c>
+      <c r="H60" s="3">
         <v>23200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
+        <v>23200</v>
+      </c>
+      <c r="J60" s="3">
         <v>13100</v>
       </c>
-      <c r="G60" s="3">
-        <v>10200</v>
-      </c>
-      <c r="H60" s="3">
-        <v>11200</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>16600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>8000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3077,16 +3355,22 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -3127,31 +3411,37 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3177,8 +3467,14 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3227,8 +3523,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3277,8 +3579,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3327,38 +3635,44 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>22700</v>
+      </c>
+      <c r="F66" s="3">
         <v>13800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
+        <v>13800</v>
+      </c>
+      <c r="H66" s="3">
         <v>23200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
+        <v>23200</v>
+      </c>
+      <c r="J66" s="3">
         <v>13100</v>
       </c>
-      <c r="G66" s="3">
-        <v>10200</v>
-      </c>
-      <c r="H66" s="3">
-        <v>11200</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>16600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>8000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3377,8 +3691,14 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3397,8 +3717,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3447,8 +3769,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3497,8 +3825,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3547,8 +3881,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3597,38 +3937,44 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F72" s="3">
         <v>12600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
+        <v>12600</v>
+      </c>
+      <c r="H72" s="3">
         <v>18000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
+        <v>18000</v>
+      </c>
+      <c r="J72" s="3">
         <v>18800</v>
       </c>
-      <c r="G72" s="3">
-        <v>29200</v>
-      </c>
-      <c r="H72" s="3">
-        <v>27500</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>23300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>16200</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,8 +3993,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3697,8 +4049,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3747,8 +4105,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3797,38 +4161,44 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>26700</v>
+      </c>
+      <c r="F76" s="3">
         <v>39500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>39500</v>
+      </c>
+      <c r="H76" s="3">
         <v>47100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
+        <v>47100</v>
+      </c>
+      <c r="J76" s="3">
         <v>46400</v>
       </c>
-      <c r="G76" s="3">
-        <v>61200</v>
-      </c>
-      <c r="H76" s="3">
-        <v>58900</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>50700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>20800</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3847,8 +4217,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3897,52 +4273,58 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
-        <v>44651</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44469</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44286</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44104</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>43921</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43738</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43555</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3952,47 +4334,53 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-5400</v>
+        <v>-6600</v>
       </c>
       <c r="E81" s="3">
-        <v>-700</v>
+        <v>-6600</v>
       </c>
       <c r="F81" s="3">
-        <v>-10500</v>
+        <v>-2700</v>
       </c>
       <c r="G81" s="3">
-        <v>1700</v>
+        <v>-2700</v>
       </c>
       <c r="H81" s="3">
-        <v>11300</v>
+        <v>-400</v>
       </c>
       <c r="I81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="K81" s="3">
         <v>7100</v>
-      </c>
-      <c r="J81" s="3">
-        <v>7600</v>
-      </c>
-      <c r="K81" s="3">
-        <v>5100</v>
       </c>
       <c r="L81" s="3">
         <v>7600</v>
       </c>
       <c r="M81" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N81" s="3">
+        <v>7600</v>
+      </c>
+      <c r="O81" s="3">
         <v>4100</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4002,8 +4390,14 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4022,31 +4416,33 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -4057,11 +4453,11 @@
       <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>400</v>
+      </c>
+      <c r="O83" s="3">
+        <v>200</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -4072,8 +4468,14 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4122,8 +4524,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4172,8 +4580,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4222,8 +4636,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4272,8 +4692,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4322,47 +4748,53 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="H89" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I89" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J89" s="3">
         <v>-3700</v>
       </c>
-      <c r="E89" s="3">
-        <v>4800</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-7400</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L89" s="3">
         <v>6100</v>
       </c>
-      <c r="H89" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="I89" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J89" s="3">
-        <v>6100</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>8400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>13200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>7700</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4372,8 +4804,14 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4392,8 +4830,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4407,13 +4847,13 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -4422,16 +4862,16 @@
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4442,8 +4882,14 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4492,8 +4938,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4542,8 +4994,14 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4554,22 +5012,22 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>-3900</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-27100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
       </c>
       <c r="L94" s="3">
         <v>-100</v>
@@ -4577,11 +5035,11 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
@@ -4592,8 +5050,14 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4612,31 +5076,33 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4662,8 +5128,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4712,8 +5184,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4762,8 +5240,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4812,47 +5296,53 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3500</v>
+        <v>3000</v>
       </c>
       <c r="E100" s="3">
-        <v>2100</v>
+        <v>3000</v>
       </c>
       <c r="F100" s="3">
-        <v>3300</v>
+        <v>-1700</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>-1700</v>
       </c>
       <c r="H100" s="3">
-        <v>26600</v>
+        <v>1000</v>
       </c>
       <c r="I100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K100" s="3">
         <v>24100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-16000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-6900</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4862,47 +5352,53 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-500</v>
+        <v>200</v>
       </c>
       <c r="E101" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F101" s="3">
-        <v>-600</v>
+        <v>-300</v>
       </c>
       <c r="G101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>600</v>
-      </c>
       <c r="I101" s="3">
+        <v>100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4912,47 +5408,53 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-7700</v>
+        <v>1800</v>
       </c>
       <c r="E102" s="3">
-        <v>7200</v>
+        <v>1800</v>
       </c>
       <c r="F102" s="3">
-        <v>-8500</v>
+        <v>-3800</v>
       </c>
       <c r="G102" s="3">
-        <v>6200</v>
+        <v>-3800</v>
       </c>
       <c r="H102" s="3">
-        <v>-2000</v>
+        <v>3600</v>
       </c>
       <c r="I102" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="K102" s="3">
         <v>25900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>6900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>8600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1000</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4960,6 +5462,12 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="92">
   <si>
     <t>UPC</t>
   </si>
@@ -656,82 +656,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44286</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44104</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43921</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43738</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43555</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -741,53 +743,59 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F8" s="3">
         <v>6400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>6400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>6900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>6900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>9200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>9200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>8000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>24300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>30700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>16400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>33200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>18100</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -797,16 +805,22 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="E9" s="3">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="F9" s="3">
         <v>4800</v>
@@ -815,35 +829,35 @@
         <v>4800</v>
       </c>
       <c r="H9" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I9" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J9" s="3">
         <v>6200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>6200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>12300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>16600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>7900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>19600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>11100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -853,53 +867,59 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F10" s="3">
         <v>1700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>3100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>3100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>4100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>12000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>14100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>8500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>13600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>7000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -909,8 +929,14 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,53 +957,55 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E12" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
         <v>1300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>3700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>300</v>
-      </c>
-      <c r="L12" s="3">
-        <v>600</v>
-      </c>
-      <c r="M12" s="3">
-        <v>500</v>
       </c>
       <c r="N12" s="3">
         <v>600</v>
       </c>
       <c r="O12" s="3">
+        <v>500</v>
+      </c>
+      <c r="P12" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q12" s="3">
         <v>300</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,8 +1015,14 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,23 +1077,29 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F14" s="3">
         <v>5400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>5400</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
@@ -1067,26 +1107,26 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1099,8 +1139,14 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1125,14 +1171,14 @@
       <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>200</v>
-      </c>
-      <c r="M15" s="3">
         <v>100</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N15" s="3">
         <v>200</v>
@@ -1140,11 +1186,11 @@
       <c r="O15" s="3">
         <v>100</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>100</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
@@ -1155,8 +1201,14 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,53 +1226,55 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F17" s="3">
         <v>7300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>7300</v>
       </c>
-      <c r="F17" s="3">
-        <v>8800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>8800</v>
-      </c>
       <c r="H17" s="3">
+        <v>9000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J17" s="3">
         <v>9200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>9200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>13000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>14700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>20500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>9800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>23500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>12900</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,53 +1284,59 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1800</v>
-      </c>
       <c r="H18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J18" s="3">
         <v>100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>9600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>10200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>6600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>9700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>5200</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1286,8 +1346,14 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,29 +1374,31 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1344,17 +1412,17 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1364,53 +1432,59 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-700</v>
       </c>
-      <c r="F21" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-1800</v>
-      </c>
       <c r="H21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J21" s="3">
         <v>200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-4900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>9800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>10600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>6800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>10200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>5500</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1420,8 +1494,14 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1438,22 +1518,22 @@
         <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3">
-        <v>100</v>
-      </c>
-      <c r="M22" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
@@ -1461,11 +1541,11 @@
       <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>100</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
@@ -1476,53 +1556,59 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-6200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-6200</v>
       </c>
-      <c r="F23" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-2100</v>
-      </c>
       <c r="H23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J23" s="3">
         <v>100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-5600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>9600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>10100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>6500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>9700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>5200</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1532,53 +1618,59 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
-        <v>700</v>
-      </c>
-      <c r="G24" s="3">
-        <v>700</v>
-      </c>
       <c r="H24" s="3">
+        <v>600</v>
+      </c>
+      <c r="I24" s="3">
+        <v>600</v>
+      </c>
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>2500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>2100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>1100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1588,8 +1680,14 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,53 +1742,59 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-6600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-6600</v>
       </c>
-      <c r="F26" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-5200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>7100</v>
-      </c>
-      <c r="L26" s="3">
-        <v>7600</v>
-      </c>
-      <c r="M26" s="3">
-        <v>5100</v>
       </c>
       <c r="N26" s="3">
         <v>7600</v>
       </c>
       <c r="O26" s="3">
+        <v>5100</v>
+      </c>
+      <c r="P26" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Q26" s="3">
         <v>4100</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1700,53 +1804,59 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-6600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-6600</v>
       </c>
-      <c r="F27" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-5200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>7100</v>
-      </c>
-      <c r="L27" s="3">
-        <v>7600</v>
-      </c>
-      <c r="M27" s="3">
-        <v>5100</v>
       </c>
       <c r="N27" s="3">
         <v>7600</v>
       </c>
       <c r="O27" s="3">
+        <v>5100</v>
+      </c>
+      <c r="P27" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Q27" s="3">
         <v>4100</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1756,8 +1866,14 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1928,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1868,8 +1990,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +2052,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,29 +2114,35 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2016,17 +2156,17 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2036,53 +2176,59 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-6600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-6600</v>
       </c>
-      <c r="F33" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-5200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>7100</v>
-      </c>
-      <c r="L33" s="3">
-        <v>7600</v>
-      </c>
-      <c r="M33" s="3">
-        <v>5100</v>
       </c>
       <c r="N33" s="3">
         <v>7600</v>
       </c>
       <c r="O33" s="3">
+        <v>5100</v>
+      </c>
+      <c r="P33" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Q33" s="3">
         <v>4100</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2092,8 +2238,14 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,53 +2300,59 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-6600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-6600</v>
       </c>
-      <c r="F35" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-5200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>7100</v>
-      </c>
-      <c r="L35" s="3">
-        <v>7600</v>
-      </c>
-      <c r="M35" s="3">
-        <v>5100</v>
       </c>
       <c r="N35" s="3">
         <v>7600</v>
       </c>
       <c r="O35" s="3">
+        <v>5100</v>
+      </c>
+      <c r="P35" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Q35" s="3">
         <v>4100</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2204,58 +2362,64 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44286</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44104</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43921</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43738</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43555</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2265,8 +2429,14 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2457,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,44 +2481,46 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>29500</v>
+      </c>
+      <c r="F41" s="3">
         <v>8900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>13000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>13000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>36000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10100</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,43 +2539,49 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>2500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>2500</v>
       </c>
-      <c r="F42" s="3">
-        <v>13200</v>
-      </c>
-      <c r="G42" s="3">
-        <v>13200</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>13300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>13300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>13100</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2421,44 +2601,50 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>18600</v>
+      </c>
+      <c r="F43" s="3">
         <v>14400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>14400</v>
       </c>
-      <c r="F43" s="3">
-        <v>10700</v>
-      </c>
-      <c r="G43" s="3">
-        <v>10700</v>
-      </c>
       <c r="H43" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I43" s="3">
+        <v>13000</v>
+      </c>
+      <c r="J43" s="3">
         <v>17500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>17500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>15200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>17800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>10900</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2477,44 +2663,50 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F44" s="3">
         <v>3400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>3400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>3300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>3300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>3100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>4900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1900</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2533,44 +2725,50 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3600</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>3100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2589,44 +2787,50 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>51600</v>
+      </c>
+      <c r="F46" s="3">
         <v>33500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>33500</v>
       </c>
-      <c r="F46" s="3">
-        <v>36800</v>
-      </c>
-      <c r="G46" s="3">
-        <v>36800</v>
-      </c>
       <c r="H46" s="3">
+        <v>25300</v>
+      </c>
+      <c r="I46" s="3">
+        <v>25300</v>
+      </c>
+      <c r="J46" s="3">
         <v>52500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>52500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>41500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>61800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>23300</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,8 +2849,14 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2672,16 +2882,16 @@
         <v>700</v>
       </c>
       <c r="K47" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L47" s="3">
         <v>700</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
+      <c r="M47" s="3">
+        <v>800</v>
+      </c>
+      <c r="N47" s="3">
+        <v>700</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
@@ -2701,44 +2911,50 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F48" s="3">
         <v>3500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4400</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2757,16 +2973,22 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E49" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F49" s="3">
         <v>100</v>
@@ -2775,10 +2997,10 @@
         <v>100</v>
       </c>
       <c r="H49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J49" s="3">
         <v>200</v>
@@ -2789,11 +3011,11 @@
       <c r="L49" s="3">
         <v>200</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>200</v>
+      </c>
+      <c r="N49" s="3">
+        <v>200</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
@@ -2813,8 +3035,14 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +3097,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,44 +3159,50 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F52" s="3">
         <v>11500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>11500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>11300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>11300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>12000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>12000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>11600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,8 +3221,14 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,44 +3283,50 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>68000</v>
+      </c>
+      <c r="F54" s="3">
         <v>49400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>49400</v>
       </c>
-      <c r="F54" s="3">
-        <v>53300</v>
-      </c>
-      <c r="G54" s="3">
-        <v>53300</v>
-      </c>
       <c r="H54" s="3">
+        <v>41700</v>
+      </c>
+      <c r="I54" s="3">
+        <v>41700</v>
+      </c>
+      <c r="J54" s="3">
         <v>70400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>70400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>59500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>67300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>28800</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3345,14 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3373,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,44 +3397,46 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F57" s="3">
         <v>7800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>11200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>11200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>8600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3193,44 +3455,50 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F58" s="3">
         <v>4400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>4400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>5500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>5500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2600</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3249,44 +3517,50 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F59" s="3">
         <v>5500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2700</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,44 +3579,50 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>20300</v>
+      </c>
+      <c r="F60" s="3">
         <v>20600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>20600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>13800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>13800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>23200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>23200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>13100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>16600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>8000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3361,8 +3641,14 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3373,10 +3659,10 @@
         <v>2100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -3417,8 +3703,14 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3443,11 +3735,11 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -3473,8 +3765,14 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3827,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3889,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,44 +3951,50 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>22500</v>
+      </c>
+      <c r="F66" s="3">
         <v>22700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>22700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>13800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>13800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>23200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>23200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>13100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>16600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>8000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3697,8 +4013,14 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +4041,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +4099,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +4161,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3887,8 +4223,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,44 +4285,50 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-500</v>
       </c>
-      <c r="F72" s="3">
-        <v>12600</v>
-      </c>
-      <c r="G72" s="3">
-        <v>12600</v>
-      </c>
       <c r="H72" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I72" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J72" s="3">
         <v>18000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>18000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>18800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>23300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>16200</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,8 +4347,14 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4409,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4471,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,44 +4533,50 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>45500</v>
+      </c>
+      <c r="F76" s="3">
         <v>26700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>26700</v>
       </c>
-      <c r="F76" s="3">
-        <v>39500</v>
-      </c>
-      <c r="G76" s="3">
-        <v>39500</v>
-      </c>
       <c r="H76" s="3">
+        <v>28000</v>
+      </c>
+      <c r="I76" s="3">
+        <v>28000</v>
+      </c>
+      <c r="J76" s="3">
         <v>47100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>47100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>46400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>50700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>20800</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,8 +4595,14 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,58 +4657,64 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44286</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44104</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43921</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43738</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43555</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4340,53 +4724,59 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-6600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-6600</v>
       </c>
-      <c r="F81" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="J81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-5200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>7100</v>
-      </c>
-      <c r="L81" s="3">
-        <v>7600</v>
-      </c>
-      <c r="M81" s="3">
-        <v>5100</v>
       </c>
       <c r="N81" s="3">
         <v>7600</v>
       </c>
       <c r="O81" s="3">
+        <v>5100</v>
+      </c>
+      <c r="P81" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Q81" s="3">
         <v>4100</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,8 +4786,14 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,8 +4814,10 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4445,10 +4843,10 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>200</v>
@@ -4459,11 +4857,11 @@
       <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>200</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4474,8 +4872,14 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4934,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4996,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +5058,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +5120,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,53 +5182,59 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>6100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>8400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>13200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>7700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4810,8 +5244,14 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,16 +5272,18 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -4859,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -4868,16 +5310,16 @@
         <v>-100</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -4888,8 +5330,14 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5392,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,16 +5454,22 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -5024,16 +5484,16 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
@@ -5041,11 +5501,11 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5056,8 +5516,14 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5544,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5104,11 +5572,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5134,8 +5602,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5664,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5726,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,53 +5788,59 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F100" s="3">
         <v>3000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>3000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>24100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-16000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-6900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,53 +5850,59 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5414,53 +5912,59 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F102" s="3">
         <v>1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-3800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>3600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>3600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-4300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>25900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>6900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>8600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,6 +5972,12 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UPC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UPC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="92">
   <si>
     <t>UPC</t>
   </si>
@@ -656,90 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43921</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43738</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43555</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -749,59 +750,65 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>5100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>5100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>6400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>6400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>6900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>6900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>9200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>9200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>8000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>24300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>30700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>16400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>33200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>18100</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,22 +818,28 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
         <v>3700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3700</v>
-      </c>
-      <c r="F9" s="3">
-        <v>4800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>4800</v>
       </c>
       <c r="H9" s="3">
         <v>4800</v>
@@ -835,35 +848,35 @@
         <v>4800</v>
       </c>
       <c r="J9" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K9" s="3">
+        <v>4800</v>
+      </c>
+      <c r="L9" s="3">
         <v>6200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>6200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>12300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>16600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>7900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>19600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>11100</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,59 +886,65 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
         <v>1400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>3100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>3100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>4100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>12000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>14100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>8500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>13600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>7000</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,8 +954,14 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,59 +984,61 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>1500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1500</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
       <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <v>1300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>3700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>300</v>
-      </c>
-      <c r="N12" s="3">
-        <v>600</v>
-      </c>
-      <c r="O12" s="3">
-        <v>500</v>
       </c>
       <c r="P12" s="3">
         <v>600</v>
       </c>
       <c r="Q12" s="3">
+        <v>500</v>
+      </c>
+      <c r="R12" s="3">
+        <v>600</v>
+      </c>
+      <c r="S12" s="3">
         <v>300</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1021,8 +1048,14 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,29 +1116,35 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-5400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-5400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>5400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>5400</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
@@ -1113,26 +1152,26 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1145,16 +1184,22 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1177,14 +1222,14 @@
       <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>200</v>
-      </c>
-      <c r="O15" s="3">
         <v>100</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P15" s="3">
         <v>200</v>
@@ -1192,11 +1237,11 @@
       <c r="Q15" s="3">
         <v>100</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
+      <c r="R15" s="3">
+        <v>200</v>
+      </c>
+      <c r="S15" s="3">
+        <v>100</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
@@ -1207,8 +1252,14 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,59 +1279,61 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
         <v>8200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>7300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>7300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>9000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>9000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>9200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>9200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>13000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>14700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>20500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>9800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>23500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>12900</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1290,59 +1343,65 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-5100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>9600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>10200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>6600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>9700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>5200</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1411,14 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,35 +1441,37 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1418,17 +1485,17 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,59 +1505,65 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-2000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-4900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>9800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>10600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>6800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>10200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>5500</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,16 +1573,22 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>100</v>
-      </c>
-      <c r="E22" s="3">
-        <v>100</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -1524,22 +1603,22 @@
         <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
-      </c>
-      <c r="O22" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
@@ -1547,11 +1626,11 @@
       <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>100</v>
+      </c>
+      <c r="S22" s="3">
+        <v>100</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1562,59 +1641,65 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3">
         <v>2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-6200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-6200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-5600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>9600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>10100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>6500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>9700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>5200</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1624,59 +1709,65 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>2500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>1500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>2100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1100</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1686,8 +1777,14 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,59 +1845,65 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3">
         <v>2200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>2200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-6600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-6600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>7100</v>
-      </c>
-      <c r="N26" s="3">
-        <v>7600</v>
-      </c>
-      <c r="O26" s="3">
-        <v>5100</v>
       </c>
       <c r="P26" s="3">
         <v>7600</v>
       </c>
       <c r="Q26" s="3">
+        <v>5100</v>
+      </c>
+      <c r="R26" s="3">
+        <v>7600</v>
+      </c>
+      <c r="S26" s="3">
         <v>4100</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1810,59 +1913,65 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3">
         <v>2200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-6600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-6600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>7100</v>
-      </c>
-      <c r="N27" s="3">
-        <v>7600</v>
-      </c>
-      <c r="O27" s="3">
-        <v>5100</v>
       </c>
       <c r="P27" s="3">
         <v>7600</v>
       </c>
       <c r="Q27" s="3">
+        <v>5100</v>
+      </c>
+      <c r="R27" s="3">
+        <v>7600</v>
+      </c>
+      <c r="S27" s="3">
         <v>4100</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1872,8 +1981,14 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +2049,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2117,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2185,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,35 +2253,41 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2162,17 +2301,17 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,59 +2321,65 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
         <v>2200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-6600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-6600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>7100</v>
-      </c>
-      <c r="N33" s="3">
-        <v>7600</v>
-      </c>
-      <c r="O33" s="3">
-        <v>5100</v>
       </c>
       <c r="P33" s="3">
         <v>7600</v>
       </c>
       <c r="Q33" s="3">
+        <v>5100</v>
+      </c>
+      <c r="R33" s="3">
+        <v>7600</v>
+      </c>
+      <c r="S33" s="3">
         <v>4100</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2244,8 +2389,14 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,59 +2457,65 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3">
         <v>2200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-6600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-6600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>7100</v>
-      </c>
-      <c r="N35" s="3">
-        <v>7600</v>
-      </c>
-      <c r="O35" s="3">
-        <v>5100</v>
       </c>
       <c r="P35" s="3">
         <v>7600</v>
       </c>
       <c r="Q35" s="3">
+        <v>5100</v>
+      </c>
+      <c r="R35" s="3">
+        <v>7600</v>
+      </c>
+      <c r="S35" s="3">
         <v>4100</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,64 +2525,70 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43921</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43738</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43555</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2435,8 +2598,14 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2628,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,50 +2654,52 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="3">
         <v>29500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>29500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>13000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>13000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>36000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>10100</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2718,14 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2557,37 +2736,37 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>2500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>2500</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>13300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>13300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>13100</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2607,50 +2786,56 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>18600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>18600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>14400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>14400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>13000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>13000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>17500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>17500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>15200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>17800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>10900</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2669,50 +2854,56 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3">
         <v>1700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>3400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>3400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>3300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>3100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>4900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1900</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2731,50 +2922,56 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3600</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
         <v>3100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,50 +2990,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="3">
         <v>51600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>51600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>33500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>33500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>25300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>25300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>52500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>52500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>41500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>61800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>23300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,16 +3058,22 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>700</v>
-      </c>
-      <c r="E47" s="3">
-        <v>700</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3">
         <v>700</v>
@@ -2888,16 +3097,16 @@
         <v>700</v>
       </c>
       <c r="M47" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="N47" s="3">
         <v>700</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>800</v>
+      </c>
+      <c r="P47" s="3">
+        <v>700</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
@@ -2917,50 +3126,56 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3">
         <v>3600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4400</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,22 +3194,28 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49" s="3">
         <v>300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>300</v>
-      </c>
-      <c r="F49" s="3">
-        <v>100</v>
-      </c>
-      <c r="G49" s="3">
-        <v>100</v>
       </c>
       <c r="H49" s="3">
         <v>100</v>
@@ -3003,10 +3224,10 @@
         <v>100</v>
       </c>
       <c r="J49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L49" s="3">
         <v>200</v>
@@ -3017,11 +3238,11 @@
       <c r="N49" s="3">
         <v>200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>200</v>
+      </c>
+      <c r="P49" s="3">
+        <v>200</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -3041,8 +3262,14 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3330,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,50 +3398,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
         <v>11800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>11800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>11500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>11500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>11300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>11300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>12000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>12000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>11600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,8 +3466,14 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,50 +3534,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" s="3">
         <v>68000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>68000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>49400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>49400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>41700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>41700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>70400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>70400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>59500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>67300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>28800</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3602,14 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3632,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,50 +3658,52 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3">
         <v>4900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>7800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>7800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>4600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>11200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>11200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>8600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3461,50 +3722,56 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3">
         <v>5900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>5900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>4400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>5500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>4100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>4100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>3900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2600</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3523,50 +3790,56 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>6900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>6900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>5500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>5500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2700</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,50 +3858,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" s="3">
         <v>20300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>20300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>20600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>20600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>13800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>13800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>23200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>23200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>13100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>16600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>8000</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,16 +3926,22 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>2100</v>
@@ -3665,10 +3950,10 @@
         <v>2100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3709,8 +3994,14 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3741,11 +4032,11 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -3771,8 +4062,14 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +4130,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4198,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,50 +4266,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3">
         <v>22500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>22500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>22700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>22700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>13800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>13800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>23200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>23200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>13100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>16600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>8000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4334,14 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4364,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4428,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4496,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4564,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,50 +4632,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
         <v>-7700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-7700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>18000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>18000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>18800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>23300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>16200</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4700,14 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4768,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4836,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,50 +4904,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="3">
         <v>45500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>45500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>26700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>26700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>28000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>28000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>47100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>47100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>46400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>50700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>20800</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4972,14 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,64 +5040,70 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43921</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43738</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43555</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4730,59 +5113,65 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3">
         <v>2200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-6600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-6600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>7100</v>
-      </c>
-      <c r="N81" s="3">
-        <v>7600</v>
-      </c>
-      <c r="O81" s="3">
-        <v>5100</v>
       </c>
       <c r="P81" s="3">
         <v>7600</v>
       </c>
       <c r="Q81" s="3">
+        <v>5100</v>
+      </c>
+      <c r="R81" s="3">
+        <v>7600</v>
+      </c>
+      <c r="S81" s="3">
         <v>4100</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4792,8 +5181,14 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,8 +5211,10 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4849,10 +5246,10 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
@@ -4863,11 +5260,11 @@
       <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>400</v>
+      </c>
+      <c r="S83" s="3">
+        <v>200</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
@@ -4878,8 +5275,14 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5343,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5411,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5479,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5547,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,59 +5615,65 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>2400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-3700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>6100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>8400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>13200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>7700</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5250,8 +5683,14 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,23 +5713,25 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
@@ -5307,7 +5748,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -5316,16 +5757,16 @@
         <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5336,8 +5777,14 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5845,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,23 +5913,29 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -5490,16 +5949,16 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
       </c>
       <c r="P94" s="3">
         <v>-100</v>
@@ -5507,11 +5966,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -5522,8 +5981,14 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +6011,10 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5578,11 +6045,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -5608,8 +6075,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +6143,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +6211,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,59 +6279,65 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>13900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>13900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>3000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>1700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>24100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-6900</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5856,59 +6347,65 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5918,59 +6415,65 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>10300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>10300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-3800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-3800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>3600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>3600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-4300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>25900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>6900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>8600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>1000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5978,6 +6481,12 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
